--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N83_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N83_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.38008897909514</v>
+        <v>5.424264459102961</v>
       </c>
       <c r="D2" t="n">
-        <v>9.358760889742991</v>
+        <v>1.520798644583236</v>
       </c>
       <c r="E2" t="n">
-        <v>8.903836639838818</v>
+        <v>1.446873453973808</v>
       </c>
       <c r="F2" t="n">
-        <v>4.058088807071308</v>
+        <v>0.6594394311490874</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.86063247435515</v>
+        <v>4.202352777082712</v>
       </c>
       <c r="D3" t="n">
-        <v>9.346168836698844</v>
+        <v>1.518752435963562</v>
       </c>
       <c r="E3" t="n">
-        <v>8.903836639838818</v>
+        <v>1.446873453973808</v>
       </c>
       <c r="F3" t="n">
-        <v>4.058088807071308</v>
+        <v>0.6594394311490874</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.2151037102585</v>
+        <v>3.284954352917006</v>
       </c>
       <c r="D4" t="n">
-        <v>8.26281281505524</v>
+        <v>1.342707082446476</v>
       </c>
       <c r="E4" t="n">
-        <v>8.903836639838818</v>
+        <v>1.446873453973808</v>
       </c>
       <c r="F4" t="n">
-        <v>4.058088807071308</v>
+        <v>0.6594394311490874</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>9.325257422181441</v>
+        <v>1.515354331104484</v>
       </c>
       <c r="D5" t="n">
-        <v>19.10207763312035</v>
+        <v>3.104087615382057</v>
       </c>
       <c r="E5" t="n">
-        <v>8.903836639838818</v>
+        <v>1.446873453973808</v>
       </c>
       <c r="F5" t="n">
-        <v>4.058088807071308</v>
+        <v>0.6594394311490874</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.70111393681034</v>
+        <v>5.313931014731681</v>
       </c>
       <c r="D6" t="n">
-        <v>9.056057136234092</v>
+        <v>1.47160928463804</v>
       </c>
       <c r="E6" t="n">
-        <v>8.903836639838818</v>
+        <v>1.446873453973808</v>
       </c>
       <c r="F6" t="n">
-        <v>4.058088807071308</v>
+        <v>0.6594394311490874</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
